--- a/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.40244670923054</v>
+        <v>45.65540520997445</v>
       </c>
       <c r="M2" t="n">
-        <v>99.56535903949631</v>
+        <v>99.31543435787037</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01590550025833</v>
+        <v>87.94789983678514</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91946759859128</v>
+        <v>45.89644111524971</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228708350063844</v>
+        <v>2.228551218804076</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700472597720053</v>
+        <v>5.683570851234288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429027833546147</v>
+        <v>0.7428504062680252</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97004163030586</v>
+        <v>33.9627649345933</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17352803431227</v>
+        <v>34.17111868832916</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557109708535346</v>
+        <v>6.516228698381144</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643142395966342</v>
+        <v>4.642815039175158</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98409449974168</v>
+        <v>12.05210016321486</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86106893709714</v>
+        <v>48.8175406982601</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646310354301</v>
+        <v>106.7660819767247</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14496755749246</v>
+        <v>86.97150787874745</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68189710041953</v>
+        <v>42.54637721652604</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186952272060647</v>
+        <v>2.181127738955125</v>
       </c>
       <c r="E4" t="n">
-        <v>6.506288250426592</v>
+        <v>6.469543950335465</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444587786952923</v>
+        <v>0.7443996615471222</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33359419740319</v>
+        <v>33.24003866969971</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24510381998344</v>
+        <v>34.24238443116762</v>
       </c>
       <c r="I4" t="n">
-        <v>5.475702872077711</v>
+        <v>5.441515542372888</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652867366845577</v>
+        <v>4.652497884669514</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85503244250754</v>
+        <v>13.02849212125256</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28092852072474</v>
+        <v>44.2441243094886</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81785806365181</v>
+        <v>99.81899364726719</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.06170706304611</v>
+        <v>85.63778836752572</v>
       </c>
       <c r="C5" t="n">
-        <v>42.44854729192792</v>
+        <v>42.05715655686748</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13435479150544</v>
+        <v>2.11541860982905</v>
       </c>
       <c r="E5" t="n">
-        <v>7.111668992145342</v>
+        <v>7.031743416202862</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457768421251115</v>
+        <v>0.7457158719441427</v>
       </c>
       <c r="G5" t="n">
-        <v>32.53190177135812</v>
+        <v>32.23864202791045</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30573473775512</v>
+        <v>34.30293010943056</v>
       </c>
       <c r="I5" t="n">
-        <v>4.57116466487502</v>
+        <v>4.542614132557757</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661105263281947</v>
+        <v>4.660724199650891</v>
       </c>
       <c r="K5" t="n">
-        <v>13.93829293695391</v>
+        <v>14.36221163247428</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46105691356045</v>
+        <v>43.42947860114788</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84789714244226</v>
+        <v>99.84884679048965</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.83475331129166</v>
+        <v>84.03166232915902</v>
       </c>
       <c r="C6" t="n">
-        <v>41.93163262661221</v>
+        <v>41.15631251704173</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074777489403892</v>
+        <v>2.036379999365828</v>
       </c>
       <c r="E6" t="n">
-        <v>7.548993125405417</v>
+        <v>7.400883094309213</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468947601962002</v>
+        <v>0.746837338727413</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62382268934054</v>
+        <v>31.03410621770825</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3571589690252</v>
+        <v>34.354517581461</v>
       </c>
       <c r="I6" t="n">
-        <v>3.81501402669416</v>
+        <v>3.791204730541002</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668092251226251</v>
+        <v>4.66773336704633</v>
       </c>
       <c r="K6" t="n">
-        <v>15.16524668870835</v>
+        <v>15.96833767084097</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77614388843292</v>
+        <v>42.74916608621292</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87302320375348</v>
+        <v>99.87381627409562</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.43212450799646</v>
+        <v>82.201683144638</v>
       </c>
       <c r="C7" t="n">
-        <v>41.12172232031391</v>
+        <v>39.91478367816482</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006773394376145</v>
+        <v>1.946795848983434</v>
       </c>
       <c r="E7" t="n">
-        <v>7.832099933113246</v>
+        <v>7.602536123730357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478446467170091</v>
+        <v>0.7477953636227368</v>
       </c>
       <c r="G7" t="n">
-        <v>30.5873021688078</v>
+        <v>29.66885806203192</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40085374898241</v>
+        <v>34.39858672664589</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183221574018529</v>
+        <v>3.163389996981556</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674029041981306</v>
+        <v>4.673721022642104</v>
       </c>
       <c r="K7" t="n">
-        <v>16.56787549200357</v>
+        <v>17.79831685536199</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20442957582991</v>
+        <v>42.18158822395817</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89402738814739</v>
+        <v>99.89468875748499</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.46736229446428</v>
+        <v>87.00115966530781</v>
       </c>
       <c r="C8" t="n">
-        <v>43.50455193460589</v>
+        <v>42.18710757096219</v>
       </c>
       <c r="D8" t="n">
-        <v>2.011091064142498</v>
+        <v>1.950949242557037</v>
       </c>
       <c r="E8" t="n">
-        <v>9.723218098912813</v>
+        <v>9.412017500921282</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494536705510444</v>
+        <v>0.7493907483978084</v>
       </c>
       <c r="G8" t="n">
-        <v>31.1143912431812</v>
+        <v>30.16475420641437</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47486884534803</v>
+        <v>34.47197442629918</v>
       </c>
       <c r="I8" t="n">
-        <v>5.710253931384665</v>
+        <v>5.568381363231819</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684085440944027</v>
+        <v>4.683692177486301</v>
       </c>
       <c r="K8" t="n">
-        <v>11.53263770553573</v>
+        <v>12.99884033469219</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77287721247469</v>
+        <v>44.62883453482762</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8100668526163</v>
+        <v>99.81478244048201</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.68857181732864</v>
+        <v>84.71283679874948</v>
       </c>
       <c r="C9" t="n">
-        <v>42.61245442345536</v>
+        <v>40.76217513218102</v>
       </c>
       <c r="D9" t="n">
-        <v>1.931137553257408</v>
+        <v>1.846817212037147</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13120370196319</v>
+        <v>9.684451523916573</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508274949988566</v>
+        <v>0.7507615647487227</v>
       </c>
       <c r="G9" t="n">
-        <v>29.87739861599485</v>
+        <v>28.5547086772286</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53806476994739</v>
+        <v>34.53503197844124</v>
       </c>
       <c r="I9" t="n">
-        <v>4.767267837424105</v>
+        <v>4.648806062697687</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692671843742853</v>
+        <v>4.692259779679516</v>
       </c>
       <c r="K9" t="n">
-        <v>13.31142818267135</v>
+        <v>15.28716320125054</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91749922911261</v>
+        <v>43.79598440647867</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84138183523932</v>
+        <v>99.84532273991022</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.70048124453496</v>
+        <v>82.29154309712109</v>
       </c>
       <c r="C10" t="n">
-        <v>41.36459732639615</v>
+        <v>39.06111278501066</v>
       </c>
       <c r="D10" t="n">
-        <v>1.842475468557528</v>
+        <v>1.737992105876659</v>
       </c>
       <c r="E10" t="n">
-        <v>10.32921880492574</v>
+        <v>9.760470161521893</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520032067699112</v>
+        <v>0.751941526124082</v>
       </c>
       <c r="G10" t="n">
-        <v>28.50567217308293</v>
+        <v>26.87210079219947</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5921475114159</v>
+        <v>34.58931020170777</v>
       </c>
       <c r="I10" t="n">
-        <v>3.978944037471002</v>
+        <v>3.880093771415694</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700020042311944</v>
+        <v>4.699634538275512</v>
       </c>
       <c r="K10" t="n">
-        <v>15.29951875546506</v>
+        <v>17.70845690287893</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20345981154366</v>
+        <v>43.10129681036883</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86757589340486</v>
+        <v>99.87086649825841</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.67717954872329</v>
+        <v>79.77947828630997</v>
       </c>
       <c r="C11" t="n">
-        <v>39.95869907383987</v>
+        <v>37.14934168760762</v>
       </c>
       <c r="D11" t="n">
-        <v>1.753174023447472</v>
+        <v>1.626405536452217</v>
       </c>
       <c r="E11" t="n">
-        <v>10.38195118387577</v>
+        <v>9.673436933713852</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530098610422887</v>
+        <v>0.7529587574303703</v>
       </c>
       <c r="G11" t="n">
-        <v>27.12405393048957</v>
+        <v>25.14679632706965</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63845360794527</v>
+        <v>34.63610284179703</v>
       </c>
       <c r="I11" t="n">
-        <v>3.320225310408615</v>
+        <v>3.237785655907038</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706311631514304</v>
+        <v>4.705992233939813</v>
       </c>
       <c r="K11" t="n">
-        <v>17.32282045127672</v>
+        <v>20.22052171369004</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60795425162034</v>
+        <v>42.52235621616303</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88947377673693</v>
+        <v>99.89221961746068</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.55853827963927</v>
+        <v>77.21220658519853</v>
       </c>
       <c r="C12" t="n">
-        <v>38.35469013399451</v>
+        <v>35.08201830576395</v>
       </c>
       <c r="D12" t="n">
-        <v>1.660464112759159</v>
+        <v>1.513605930229576</v>
       </c>
       <c r="E12" t="n">
-        <v>10.29461231120468</v>
+        <v>9.452751101610668</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538729421966086</v>
+        <v>0.7538368433020807</v>
       </c>
       <c r="G12" t="n">
-        <v>25.68970195871224</v>
+        <v>23.40273639866953</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67815534104398</v>
+        <v>34.67649479189571</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770025724993816</v>
+        <v>2.70130124885296</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711705888728804</v>
+        <v>4.711480270638003</v>
       </c>
       <c r="K12" t="n">
-        <v>19.44146172036072</v>
+        <v>22.78779341480148</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11161966480008</v>
+        <v>42.04024978899271</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9077715191553</v>
+        <v>99.91006150955815</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.38694876666648</v>
+        <v>74.7216690670048</v>
       </c>
       <c r="C13" t="n">
-        <v>36.61178760703792</v>
+        <v>33.00757348462548</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56621542180934</v>
+        <v>1.405334555187836</v>
       </c>
       <c r="E13" t="n">
-        <v>10.09538929514843</v>
+        <v>9.152134055076752</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546136760843831</v>
+        <v>0.7545946137341945</v>
       </c>
       <c r="G13" t="n">
-        <v>24.23154290432814</v>
+        <v>21.72869007061438</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7122290998816</v>
+        <v>34.71135223177294</v>
       </c>
       <c r="I13" t="n">
-        <v>2.310622893887188</v>
+        <v>2.253347204779988</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716335475527394</v>
+        <v>4.716216335838714</v>
       </c>
       <c r="K13" t="n">
-        <v>21.61305123333352</v>
+        <v>25.27833093299521</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69821600060096</v>
+        <v>41.63905943657785</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9230548409724</v>
+        <v>99.92496385419852</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.81311896103412</v>
+        <v>82.26095781159707</v>
       </c>
       <c r="C14" t="n">
-        <v>40.32769114736307</v>
+        <v>37.78882358505052</v>
       </c>
       <c r="D14" t="n">
-        <v>1.568302598907013</v>
+        <v>1.406937186527689</v>
       </c>
       <c r="E14" t="n">
-        <v>12.23381967398073</v>
+        <v>11.77383775102741</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556192927833267</v>
+        <v>0.7554551468879482</v>
       </c>
       <c r="G14" t="n">
-        <v>25.82369125234136</v>
+        <v>23.89568754732398</v>
       </c>
       <c r="H14" t="n">
-        <v>36.31834426745914</v>
+        <v>36.89315502382714</v>
       </c>
       <c r="I14" t="n">
-        <v>3.390721295666768</v>
+        <v>2.814290487953217</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722620579895792</v>
+        <v>4.721594668049676</v>
       </c>
       <c r="K14" t="n">
-        <v>15.18688103896589</v>
+        <v>17.73904218840294</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37255418864417</v>
+        <v>44.37843140150388</v>
       </c>
       <c r="M14" t="n">
-        <v>99.88712637497312</v>
+        <v>99.90629717495734</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.38233788588767</v>
+        <v>81.40001416235782</v>
       </c>
       <c r="C15" t="n">
-        <v>40.41429087071046</v>
+        <v>37.35605862244748</v>
       </c>
       <c r="D15" t="n">
-        <v>1.552119603643854</v>
+        <v>1.374928457145514</v>
       </c>
       <c r="E15" t="n">
-        <v>12.58634366746929</v>
+        <v>11.90301937038305</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564636497736335</v>
+        <v>0.7561813663994026</v>
       </c>
       <c r="G15" t="n">
-        <v>25.56452437562393</v>
+        <v>23.35783983134675</v>
       </c>
       <c r="H15" t="n">
-        <v>36.3662302672462</v>
+        <v>36.9344150411012</v>
       </c>
       <c r="I15" t="n">
-        <v>2.828758511045551</v>
+        <v>2.347496555985644</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727897811085208</v>
+        <v>4.726133539996265</v>
       </c>
       <c r="K15" t="n">
-        <v>15.61766211411235</v>
+        <v>18.59998583764218</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87386031251979</v>
+        <v>43.96578080413387</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90581329734259</v>
+        <v>99.92182526422353</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.24956953822779</v>
+        <v>78.80259444375501</v>
       </c>
       <c r="C16" t="n">
-        <v>38.71956607538495</v>
+        <v>35.12059049500322</v>
       </c>
       <c r="D16" t="n">
-        <v>1.47014721162317</v>
+        <v>1.278506141313559</v>
       </c>
       <c r="E16" t="n">
-        <v>12.3148774954945</v>
+        <v>11.39458409512336</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571870237850621</v>
+        <v>0.7568076159694597</v>
       </c>
       <c r="G16" t="n">
-        <v>24.21438021854915</v>
+        <v>21.71977859429435</v>
       </c>
       <c r="H16" t="n">
-        <v>36.40100574638102</v>
+        <v>36.96500315470408</v>
       </c>
       <c r="I16" t="n">
-        <v>2.359552943738267</v>
+        <v>1.957867242541079</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732418898656637</v>
+        <v>4.730047599809122</v>
       </c>
       <c r="K16" t="n">
-        <v>17.7504304617722</v>
+        <v>21.19740555624501</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45142683753603</v>
+        <v>43.6167957110855</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92142337469318</v>
+        <v>99.93479176233373</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.98493623268558</v>
+        <v>80.7728344589768</v>
       </c>
       <c r="C17" t="n">
-        <v>39.96248804793105</v>
+        <v>36.54575538843397</v>
       </c>
       <c r="D17" t="n">
-        <v>1.471552676910676</v>
+        <v>1.279525519788231</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1308996738334</v>
+        <v>12.26326974052116</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579108969248854</v>
+        <v>0.7574110337930099</v>
       </c>
       <c r="G17" t="n">
-        <v>24.64032906260378</v>
+        <v>22.2746877548196</v>
       </c>
       <c r="H17" t="n">
-        <v>36.83860504218347</v>
+        <v>37.53206763717596</v>
       </c>
       <c r="I17" t="n">
-        <v>2.408695774448843</v>
+        <v>1.932053811672519</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736943105780533</v>
+        <v>4.733818961206311</v>
       </c>
       <c r="K17" t="n">
-        <v>16.01506376731441</v>
+        <v>19.22716554102321</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94223500965008</v>
+        <v>44.16272858474763</v>
       </c>
       <c r="M17" t="n">
-        <v>99.91978682489554</v>
+        <v>99.93564951420481</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.850606906176</v>
+        <v>78.22276443214979</v>
       </c>
       <c r="C18" t="n">
-        <v>38.2009040635477</v>
+        <v>34.29316482927173</v>
       </c>
       <c r="D18" t="n">
-        <v>1.392656552522483</v>
+        <v>1.189244050101581</v>
       </c>
       <c r="E18" t="n">
-        <v>12.76171172101211</v>
+        <v>11.66651620851305</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585309528379792</v>
+        <v>0.7579310456592562</v>
       </c>
       <c r="G18" t="n">
-        <v>23.3192574508349</v>
+        <v>20.7030180098901</v>
       </c>
       <c r="H18" t="n">
-        <v>36.86874314282197</v>
+        <v>37.55783583920274</v>
       </c>
       <c r="I18" t="n">
-        <v>2.008888630909176</v>
+        <v>1.611150243412718</v>
       </c>
       <c r="J18" t="n">
-        <v>4.74081845523737</v>
+        <v>4.73706903537035</v>
       </c>
       <c r="K18" t="n">
-        <v>18.14939309382402</v>
+        <v>21.77723556785022</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58279462667137</v>
+        <v>43.8759314414427</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93309178404309</v>
+        <v>99.94633183856465</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>81.04182351246335</v>
+        <v>77.253504558701</v>
       </c>
       <c r="C19" t="n">
-        <v>37.70238559334337</v>
+        <v>33.55684015835789</v>
       </c>
       <c r="D19" t="n">
-        <v>1.363538095871248</v>
+        <v>1.154980004758101</v>
       </c>
       <c r="E19" t="n">
-        <v>12.77408714148873</v>
+        <v>11.55660765832315</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590536096384927</v>
+        <v>0.7583749379521197</v>
       </c>
       <c r="G19" t="n">
-        <v>22.83168513015668</v>
+        <v>20.10653056244215</v>
       </c>
       <c r="H19" t="n">
-        <v>36.89414711514226</v>
+        <v>37.57983208010241</v>
       </c>
       <c r="I19" t="n">
-        <v>1.675227359925379</v>
+        <v>1.357335952922323</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744085060240579</v>
+        <v>4.739843362200748</v>
       </c>
       <c r="K19" t="n">
-        <v>18.95817648753663</v>
+        <v>22.74649544129901</v>
       </c>
       <c r="L19" t="n">
-        <v>43.28363545715032</v>
+        <v>43.65144635112472</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94419753803032</v>
+        <v>99.95478195078161</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.6204998795713</v>
+        <v>74.57927289971789</v>
       </c>
       <c r="C20" t="n">
-        <v>35.53971081091937</v>
+        <v>31.09078038684275</v>
       </c>
       <c r="D20" t="n">
-        <v>1.274987122890727</v>
+        <v>1.061401389262258</v>
       </c>
       <c r="E20" t="n">
-        <v>12.17731986831004</v>
+        <v>10.80888417500234</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595031462141372</v>
+        <v>0.7587585306169558</v>
       </c>
       <c r="G20" t="n">
-        <v>21.34894846208548</v>
+        <v>18.47746228012824</v>
       </c>
       <c r="H20" t="n">
-        <v>36.91599704556202</v>
+        <v>37.59884028727051</v>
       </c>
       <c r="I20" t="n">
-        <v>1.396849570670524</v>
+        <v>1.131685421081617</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746894663838357</v>
+        <v>4.742240816355973</v>
       </c>
       <c r="K20" t="n">
-        <v>21.37950012042871</v>
+        <v>25.4207271002821</v>
       </c>
       <c r="L20" t="n">
-        <v>43.03425497532066</v>
+        <v>43.45078873640509</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95346590666873</v>
+        <v>99.96229622352993</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.94922025120509</v>
+        <v>81.00762923992446</v>
       </c>
       <c r="C21" t="n">
-        <v>38.59607669446918</v>
+        <v>35.18600014926134</v>
       </c>
       <c r="D21" t="n">
-        <v>1.27614594601904</v>
+        <v>1.062064191575482</v>
       </c>
       <c r="E21" t="n">
-        <v>13.89817767657815</v>
+        <v>12.98311949784759</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7601934510776589</v>
+        <v>0.7592323446842438</v>
       </c>
       <c r="G21" t="n">
-        <v>22.69663921142915</v>
+        <v>20.4035563516029</v>
       </c>
       <c r="H21" t="n">
-        <v>38.2778365306962</v>
+        <v>39.53687488727979</v>
       </c>
       <c r="I21" t="n">
-        <v>2.289018366169532</v>
+        <v>1.517579812657913</v>
       </c>
       <c r="J21" t="n">
-        <v>4.751209069235368</v>
+        <v>4.745202154276523</v>
       </c>
       <c r="K21" t="n">
-        <v>16.05077974879491</v>
+        <v>18.99237076007554</v>
       </c>
       <c r="L21" t="n">
-        <v>45.27691223042534</v>
+        <v>45.77107466610484</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92376867368942</v>
+        <v>99.94944557544173</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.65540520997445</v>
+        <v>45.3584178384645</v>
       </c>
       <c r="M2" t="n">
-        <v>99.31543435787037</v>
+        <v>99.4435971088453</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94789983678514</v>
+        <v>87.9594942771723</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89644111524971</v>
+        <v>45.90339645684968</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228551218804076</v>
+        <v>2.228575724913623</v>
       </c>
       <c r="E3" t="n">
-        <v>5.683570851234288</v>
+        <v>5.688170645266658</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428504062680252</v>
+        <v>0.7428585749712077</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9627649345933</v>
+        <v>33.96505965269068</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17111868832916</v>
+        <v>34.17149444867555</v>
       </c>
       <c r="I3" t="n">
-        <v>6.516228698381144</v>
+        <v>6.520469137084535</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642815039175158</v>
+        <v>4.642866093570047</v>
       </c>
       <c r="K3" t="n">
-        <v>12.05210016321486</v>
+        <v>12.0405057228277</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8175406982601</v>
+        <v>48.82203014869931</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7660819767247</v>
+        <v>106.7659323283767</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97150787874745</v>
+        <v>87.0008495261395</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54637721652604</v>
+        <v>42.57164056029336</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181127738955125</v>
+        <v>2.182108069068279</v>
       </c>
       <c r="E4" t="n">
-        <v>6.469543950335465</v>
+        <v>6.477077588445982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443996615471222</v>
+        <v>0.7444083336457756</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24003866969971</v>
+        <v>33.25685993344221</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24238443116762</v>
+        <v>34.24278334770568</v>
       </c>
       <c r="I4" t="n">
-        <v>5.441515542372888</v>
+        <v>5.445060168545472</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652497884669514</v>
+        <v>4.652552085286097</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02849212125256</v>
+        <v>12.99915047386048</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2441243094886</v>
+        <v>44.24808482314938</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81899364726719</v>
+        <v>99.81887585730323</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.63778836752572</v>
+        <v>85.70191208719528</v>
       </c>
       <c r="C5" t="n">
-        <v>42.05715655686748</v>
+        <v>42.11777484240046</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11541860982905</v>
+        <v>2.11822503029509</v>
       </c>
       <c r="E5" t="n">
-        <v>7.031743416202862</v>
+        <v>7.045051129560781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457158719441427</v>
+        <v>0.7457244310795343</v>
       </c>
       <c r="G5" t="n">
-        <v>32.23864202791045</v>
+        <v>32.28323754382805</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30293010943056</v>
+        <v>34.30332382965858</v>
       </c>
       <c r="I5" t="n">
-        <v>4.542614132557757</v>
+        <v>4.545572428526157</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660724199650891</v>
+        <v>4.66077769424709</v>
       </c>
       <c r="K5" t="n">
-        <v>14.36221163247428</v>
+        <v>14.2980879128047</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42947860114788</v>
+        <v>43.43288557344633</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84884679048965</v>
+        <v>99.84874832865151</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.03166232915902</v>
+        <v>84.23296329901353</v>
       </c>
       <c r="C6" t="n">
-        <v>41.15631251704173</v>
+        <v>41.35461885054364</v>
       </c>
       <c r="D6" t="n">
-        <v>2.036379999365828</v>
+        <v>2.046218122389578</v>
       </c>
       <c r="E6" t="n">
-        <v>7.400883094309213</v>
+        <v>7.437839066587557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746837338727413</v>
+        <v>0.7468439562772405</v>
       </c>
       <c r="G6" t="n">
-        <v>31.03410621770825</v>
+        <v>31.1858016815078</v>
       </c>
       <c r="H6" t="n">
-        <v>34.354517581461</v>
+        <v>34.35482198875307</v>
       </c>
       <c r="I6" t="n">
-        <v>3.791204730541002</v>
+        <v>3.79366375676552</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66773336704633</v>
+        <v>4.667774726732754</v>
       </c>
       <c r="K6" t="n">
-        <v>15.96833767084097</v>
+        <v>15.76703670098648</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74916608621292</v>
+        <v>42.75207854767746</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87381627409562</v>
+        <v>99.8737340992076</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.201683144638</v>
+        <v>82.55014516577369</v>
       </c>
       <c r="C7" t="n">
-        <v>39.91478367816482</v>
+        <v>40.26078243751755</v>
       </c>
       <c r="D7" t="n">
-        <v>1.946795848983434</v>
+        <v>1.964057901255347</v>
       </c>
       <c r="E7" t="n">
-        <v>7.602536123730357</v>
+        <v>7.666764456093075</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477953636227368</v>
+        <v>0.7477985599873346</v>
       </c>
       <c r="G7" t="n">
-        <v>29.66885806203192</v>
+        <v>29.93362219274011</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39858672664589</v>
+        <v>34.39873375941739</v>
       </c>
       <c r="I7" t="n">
-        <v>3.163389996981556</v>
+        <v>3.165427296359589</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673721022642104</v>
+        <v>4.673740999920841</v>
       </c>
       <c r="K7" t="n">
-        <v>17.79831685536199</v>
+        <v>17.44985483422631</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18158822395817</v>
+        <v>42.18398317945709</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89468875748499</v>
+        <v>99.89462045120095</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.00115966530781</v>
+        <v>87.56152382063524</v>
       </c>
       <c r="C8" t="n">
-        <v>42.18710757096219</v>
+        <v>42.54346141148125</v>
       </c>
       <c r="D8" t="n">
-        <v>1.950949242557037</v>
+        <v>1.968369381315557</v>
       </c>
       <c r="E8" t="n">
-        <v>9.412017500921282</v>
+        <v>9.494695580112486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493907483978084</v>
+        <v>0.7494401198305445</v>
       </c>
       <c r="G8" t="n">
-        <v>30.16475420641437</v>
+        <v>30.4243473068587</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47197442629918</v>
+        <v>34.47424551220504</v>
       </c>
       <c r="I8" t="n">
-        <v>5.568381363231819</v>
+        <v>5.766425171372001</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683692177486301</v>
+        <v>4.684000748940902</v>
       </c>
       <c r="K8" t="n">
-        <v>12.99884033469219</v>
+        <v>12.43847617936476</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62883453482762</v>
+        <v>44.82626925915993</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81478244048201</v>
+        <v>99.80820685000594</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.71283679874948</v>
+        <v>85.52717539677772</v>
       </c>
       <c r="C9" t="n">
-        <v>40.76217513218102</v>
+        <v>41.40339634917254</v>
       </c>
       <c r="D9" t="n">
-        <v>1.846817212037147</v>
+        <v>1.876285446609198</v>
       </c>
       <c r="E9" t="n">
-        <v>9.684451523916573</v>
+        <v>9.852911423593387</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507615647487227</v>
+        <v>0.7508463327853808</v>
       </c>
       <c r="G9" t="n">
-        <v>28.5547086772286</v>
+        <v>29.00104046339625</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53503197844124</v>
+        <v>34.53893130812752</v>
       </c>
       <c r="I9" t="n">
-        <v>4.648806062697687</v>
+        <v>4.814370842357364</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692259779679516</v>
+        <v>4.69278957990863</v>
       </c>
       <c r="K9" t="n">
-        <v>15.28716320125054</v>
+        <v>14.47282460322228</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79598440647867</v>
+        <v>43.96360057062262</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84532273991022</v>
+        <v>99.83982152301743</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.29154309712109</v>
+        <v>83.38030916652987</v>
       </c>
       <c r="C10" t="n">
-        <v>39.06111278501066</v>
+        <v>40.00288005313045</v>
       </c>
       <c r="D10" t="n">
-        <v>1.737992105876659</v>
+        <v>1.780242879912457</v>
       </c>
       <c r="E10" t="n">
-        <v>9.760470161521893</v>
+        <v>10.01830124006451</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751941526124082</v>
+        <v>0.7520525394405636</v>
       </c>
       <c r="G10" t="n">
-        <v>26.87210079219947</v>
+        <v>27.5165465299096</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58931020170777</v>
+        <v>34.59441681426593</v>
       </c>
       <c r="I10" t="n">
-        <v>3.880093771415694</v>
+        <v>4.018420791433296</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699634538275512</v>
+        <v>4.700328371503522</v>
       </c>
       <c r="K10" t="n">
-        <v>17.70845690287893</v>
+        <v>16.61969083347012</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10129681036883</v>
+        <v>43.24369659000062</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87086649825841</v>
+        <v>99.86626747660119</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.77947828630997</v>
+        <v>81.23770360163019</v>
       </c>
       <c r="C11" t="n">
-        <v>37.14934168760762</v>
+        <v>38.48265162323762</v>
       </c>
       <c r="D11" t="n">
-        <v>1.626405536452217</v>
+        <v>1.685538646818642</v>
       </c>
       <c r="E11" t="n">
-        <v>9.673436933713852</v>
+        <v>10.04423591409931</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529587574303703</v>
+        <v>0.753087301741303</v>
       </c>
       <c r="G11" t="n">
-        <v>25.14679632706965</v>
+        <v>26.05273871699281</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63610284179703</v>
+        <v>34.64201588009994</v>
       </c>
       <c r="I11" t="n">
-        <v>3.237785655907038</v>
+        <v>3.353291505995042</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705992233939813</v>
+        <v>4.706795635883143</v>
       </c>
       <c r="K11" t="n">
-        <v>20.22052171369004</v>
+        <v>18.76229639836982</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52235621616303</v>
+        <v>42.64342917863053</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89221961746068</v>
+        <v>99.88837720023795</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.21220658519853</v>
+        <v>79.04454299882936</v>
       </c>
       <c r="C12" t="n">
-        <v>35.08201830576395</v>
+        <v>36.80817490823944</v>
       </c>
       <c r="D12" t="n">
-        <v>1.513605930229576</v>
+        <v>1.589571396132295</v>
       </c>
       <c r="E12" t="n">
-        <v>9.452751101610668</v>
+        <v>9.938645146922459</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538368433020807</v>
+        <v>0.7539757953728787</v>
       </c>
       <c r="G12" t="n">
-        <v>23.40273639866953</v>
+        <v>24.5694089148322</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67649479189571</v>
+        <v>34.68288658715242</v>
       </c>
       <c r="I12" t="n">
-        <v>2.70130124885296</v>
+        <v>2.79770643733662</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711480270638003</v>
+        <v>4.712348721080491</v>
       </c>
       <c r="K12" t="n">
-        <v>22.78779341480148</v>
+        <v>20.95545700117064</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04024978899271</v>
+        <v>42.14322110431229</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91006150955815</v>
+        <v>99.90685301372235</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.7216690670048</v>
+        <v>76.79871418659341</v>
       </c>
       <c r="C13" t="n">
-        <v>33.00757348462548</v>
+        <v>34.99434277954287</v>
       </c>
       <c r="D13" t="n">
-        <v>1.405334555187836</v>
+        <v>1.492185519915634</v>
       </c>
       <c r="E13" t="n">
-        <v>9.152134055076752</v>
+        <v>9.718713084621035</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545946137341945</v>
+        <v>0.7547395305421001</v>
       </c>
       <c r="G13" t="n">
-        <v>21.72869007061438</v>
+        <v>23.06415194989293</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71135223177294</v>
+        <v>34.71801840493661</v>
       </c>
       <c r="I13" t="n">
-        <v>2.253347204779988</v>
+        <v>2.333783630797005</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716216335838714</v>
+        <v>4.717122065888124</v>
       </c>
       <c r="K13" t="n">
-        <v>25.27833093299521</v>
+        <v>23.20128581340657</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63905943657785</v>
+        <v>41.72665733934677</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92496385419852</v>
+        <v>99.92228593229621</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.26095781159707</v>
+        <v>83.55899517372106</v>
       </c>
       <c r="C14" t="n">
-        <v>37.78882358505052</v>
+        <v>38.99358849503952</v>
       </c>
       <c r="D14" t="n">
-        <v>1.406937186527689</v>
+        <v>1.494160872580554</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77383775102741</v>
+        <v>11.99263968124786</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554551468879482</v>
+        <v>0.7557386534548199</v>
       </c>
       <c r="G14" t="n">
-        <v>23.89568754732398</v>
+        <v>24.80266893418793</v>
       </c>
       <c r="H14" t="n">
-        <v>36.89315502382714</v>
+        <v>36.47196275791421</v>
       </c>
       <c r="I14" t="n">
-        <v>2.814290487953217</v>
+        <v>3.318457690243059</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721594668049676</v>
+        <v>4.723366584092624</v>
       </c>
       <c r="K14" t="n">
-        <v>17.73904218840294</v>
+        <v>16.44100482627893</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37843140150388</v>
+        <v>44.45493766103865</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90629717495734</v>
+        <v>99.8895309823571</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.40001416235782</v>
+        <v>83.11013030586238</v>
       </c>
       <c r="C15" t="n">
-        <v>37.35605862244748</v>
+        <v>39.05724017503512</v>
       </c>
       <c r="D15" t="n">
-        <v>1.374928457145514</v>
+        <v>1.478284525245786</v>
       </c>
       <c r="E15" t="n">
-        <v>11.90301937038305</v>
+        <v>12.32661941724566</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561813663994026</v>
+        <v>0.7565777914961213</v>
       </c>
       <c r="G15" t="n">
-        <v>23.35783983134675</v>
+        <v>24.53912583514508</v>
       </c>
       <c r="H15" t="n">
-        <v>36.9344150411012</v>
+        <v>36.51245957682269</v>
       </c>
       <c r="I15" t="n">
-        <v>2.347496555985644</v>
+        <v>2.768451963056286</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726133539996265</v>
+        <v>4.728611196850757</v>
       </c>
       <c r="K15" t="n">
-        <v>18.59998583764218</v>
+        <v>16.88986969413762</v>
       </c>
       <c r="L15" t="n">
-        <v>43.96578080413387</v>
+        <v>43.96071075054272</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92182526422353</v>
+        <v>99.90782061971545</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.80259444375501</v>
+        <v>80.9558125960943</v>
       </c>
       <c r="C16" t="n">
-        <v>35.12059049500322</v>
+        <v>37.33079707645574</v>
       </c>
       <c r="D16" t="n">
-        <v>1.278506141313559</v>
+        <v>1.396555327209588</v>
       </c>
       <c r="E16" t="n">
-        <v>11.39458409512336</v>
+        <v>12.02999641579192</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568076159694597</v>
+        <v>0.7572971622615658</v>
       </c>
       <c r="G16" t="n">
-        <v>21.71977859429435</v>
+        <v>23.18244311218801</v>
       </c>
       <c r="H16" t="n">
-        <v>36.96500315470408</v>
+        <v>36.54717642456692</v>
       </c>
       <c r="I16" t="n">
-        <v>1.957867242541079</v>
+        <v>2.309236889941515</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730047599809122</v>
+        <v>4.733107264134786</v>
       </c>
       <c r="K16" t="n">
-        <v>21.19740555624501</v>
+        <v>19.04418740390569</v>
       </c>
       <c r="L16" t="n">
-        <v>43.6167957110855</v>
+        <v>43.54811407622035</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93479176233373</v>
+        <v>99.92309855658178</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.7728344589768</v>
+        <v>82.84621688800675</v>
       </c>
       <c r="C17" t="n">
-        <v>36.54575538843397</v>
+        <v>38.68300404548086</v>
       </c>
       <c r="D17" t="n">
-        <v>1.279525519788231</v>
+        <v>1.397872360235343</v>
       </c>
       <c r="E17" t="n">
-        <v>12.26326974052116</v>
+        <v>12.89564030648685</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574110337930099</v>
+        <v>0.7580113375996831</v>
       </c>
       <c r="G17" t="n">
-        <v>22.2746877548196</v>
+        <v>23.66796036733777</v>
       </c>
       <c r="H17" t="n">
-        <v>37.53206763717596</v>
+        <v>37.04529740175323</v>
       </c>
       <c r="I17" t="n">
-        <v>1.932053811672519</v>
+        <v>2.343864254595857</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733818961206311</v>
+        <v>4.737570859998018</v>
       </c>
       <c r="K17" t="n">
-        <v>19.22716554102321</v>
+        <v>17.15378311199325</v>
       </c>
       <c r="L17" t="n">
-        <v>44.16272858474763</v>
+        <v>44.08515764463785</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93564951420481</v>
+        <v>99.92194480211195</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.22276443214979</v>
+        <v>80.79346097824303</v>
       </c>
       <c r="C18" t="n">
-        <v>34.29316482927173</v>
+        <v>36.99226516392311</v>
       </c>
       <c r="D18" t="n">
-        <v>1.189244050101581</v>
+        <v>1.323349227833779</v>
       </c>
       <c r="E18" t="n">
-        <v>11.66651620851305</v>
+        <v>12.53394938113172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579310456592562</v>
+        <v>0.7586226730222992</v>
       </c>
       <c r="G18" t="n">
-        <v>20.7030180098901</v>
+        <v>22.40617810859625</v>
       </c>
       <c r="H18" t="n">
-        <v>37.55783583920274</v>
+        <v>37.07517439886354</v>
       </c>
       <c r="I18" t="n">
-        <v>1.611150243412718</v>
+        <v>1.954795482406066</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73706903537035</v>
+        <v>4.741391706389369</v>
       </c>
       <c r="K18" t="n">
-        <v>21.77723556785022</v>
+        <v>19.20653902175698</v>
       </c>
       <c r="L18" t="n">
-        <v>43.8759314414427</v>
+        <v>43.73608847391446</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94633183856465</v>
+        <v>99.93489265959455</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.253504558701</v>
+        <v>80.0649452768296</v>
       </c>
       <c r="C19" t="n">
-        <v>33.55684015835789</v>
+        <v>36.56508306172707</v>
       </c>
       <c r="D19" t="n">
-        <v>1.154980004758101</v>
+        <v>1.297643841416035</v>
       </c>
       <c r="E19" t="n">
-        <v>11.55660765832315</v>
+        <v>12.56216741013816</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583749379521197</v>
+        <v>0.7591375184624201</v>
       </c>
       <c r="G19" t="n">
-        <v>20.10653056244215</v>
+        <v>21.97094948238617</v>
       </c>
       <c r="H19" t="n">
-        <v>37.57983208010241</v>
+        <v>37.1003357671692</v>
       </c>
       <c r="I19" t="n">
-        <v>1.357335952922323</v>
+        <v>1.630101766867517</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739843362200748</v>
+        <v>4.744609490390125</v>
       </c>
       <c r="K19" t="n">
-        <v>22.74649544129901</v>
+        <v>19.93505472317037</v>
       </c>
       <c r="L19" t="n">
-        <v>43.65144635112472</v>
+        <v>43.4455623405913</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95478195078161</v>
+        <v>99.94570012548874</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.57927289971789</v>
+        <v>77.78970570232946</v>
       </c>
       <c r="C20" t="n">
-        <v>31.09078038684275</v>
+        <v>34.54106170107867</v>
       </c>
       <c r="D20" t="n">
-        <v>1.061401389262258</v>
+        <v>1.215951748079316</v>
       </c>
       <c r="E20" t="n">
-        <v>10.80888417500234</v>
+        <v>11.99786145158613</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587585306169558</v>
+        <v>0.7595796621375974</v>
       </c>
       <c r="G20" t="n">
-        <v>18.47746228012824</v>
+        <v>20.58778655391049</v>
       </c>
       <c r="H20" t="n">
-        <v>37.59884028727051</v>
+        <v>37.12194407713606</v>
       </c>
       <c r="I20" t="n">
-        <v>1.131685421081617</v>
+        <v>1.359209321119886</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742240816355973</v>
+        <v>4.747372888359983</v>
       </c>
       <c r="K20" t="n">
-        <v>25.4207271002821</v>
+        <v>22.21029429767053</v>
       </c>
       <c r="L20" t="n">
-        <v>43.45078873640509</v>
+        <v>43.20336339661559</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96229622352993</v>
+        <v>99.95471939536479</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.00762923992446</v>
+        <v>83.13635278704284</v>
       </c>
       <c r="C21" t="n">
-        <v>35.18600014926134</v>
+        <v>37.67980261538291</v>
       </c>
       <c r="D21" t="n">
-        <v>1.062064191575482</v>
+        <v>1.216993354242741</v>
       </c>
       <c r="E21" t="n">
-        <v>12.98311949784759</v>
+        <v>13.74682661213353</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592323446842438</v>
+        <v>0.7602303317541712</v>
       </c>
       <c r="G21" t="n">
-        <v>20.4035563516029</v>
+        <v>21.9880295146847</v>
       </c>
       <c r="H21" t="n">
-        <v>39.53687488727979</v>
+        <v>38.53635049498038</v>
       </c>
       <c r="I21" t="n">
-        <v>1.517579812657913</v>
+        <v>2.136482905783731</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745202154276523</v>
+        <v>4.751439573463569</v>
       </c>
       <c r="K21" t="n">
-        <v>18.99237076007554</v>
+        <v>16.86364721295718</v>
       </c>
       <c r="L21" t="n">
-        <v>45.77107466610484</v>
+        <v>45.38539502757816</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94944557544173</v>
+        <v>99.92884485591824</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_11_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.3584178384645</v>
+        <v>43.80097494374363</v>
       </c>
       <c r="M2" t="n">
-        <v>99.4435971088453</v>
+        <v>97.38862984389203</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9594942771723</v>
+        <v>81.54762543339388</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90339645684968</v>
+        <v>43.30318098894943</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228575724913623</v>
+        <v>2.183796710188704</v>
       </c>
       <c r="E3" t="n">
-        <v>5.688170645266658</v>
+        <v>4.160595965631253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428585749712077</v>
+        <v>0.7376828547196312</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96505965269068</v>
+        <v>32.84794218242176</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17149444867555</v>
+        <v>33.93341131710303</v>
       </c>
       <c r="I3" t="n">
-        <v>6.520469137084535</v>
+        <v>3.073678561331797</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642866093570047</v>
+        <v>4.610517841997695</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0405057228277</v>
+        <v>18.45237456660612</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82203014869931</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7659323283767</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0008495261395</v>
+        <v>88.76434692413414</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57164056029336</v>
+        <v>42.92619906624036</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182108069068279</v>
+        <v>2.189600925203664</v>
       </c>
       <c r="E4" t="n">
-        <v>6.477077588445982</v>
+        <v>6.567622011849672</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444083336457756</v>
+        <v>0.739643508786773</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25685993344221</v>
+        <v>33.54342423341212</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24278334770568</v>
+        <v>34.02360140419155</v>
       </c>
       <c r="I4" t="n">
-        <v>5.445060168545472</v>
+        <v>7.077682910773031</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652552085286097</v>
+        <v>4.622771929917331</v>
       </c>
       <c r="K4" t="n">
-        <v>12.99915047386048</v>
+        <v>11.23565307586586</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24808482314938</v>
+        <v>45.60285048051335</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81887585730323</v>
+        <v>99.76470262261957</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.70191208719528</v>
+        <v>87.86995620918785</v>
       </c>
       <c r="C5" t="n">
-        <v>42.11777484240046</v>
+        <v>43.12891147969109</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11822503029509</v>
+        <v>2.14811097057959</v>
       </c>
       <c r="E5" t="n">
-        <v>7.045051129560781</v>
+        <v>7.428390382324942</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457244310795343</v>
+        <v>0.741302115544753</v>
       </c>
       <c r="G5" t="n">
-        <v>32.28323754382805</v>
+        <v>32.90782204062857</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30332382965858</v>
+        <v>34.09989731505863</v>
       </c>
       <c r="I5" t="n">
-        <v>4.545572428526157</v>
+        <v>5.911295162896656</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66077769424709</v>
+        <v>4.633138222154706</v>
       </c>
       <c r="K5" t="n">
-        <v>14.2980879128047</v>
+        <v>12.13004379081213</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43288557344633</v>
+        <v>44.54444242641975</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84874832865151</v>
+        <v>99.80339769692297</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.23296329901353</v>
+        <v>86.76775749606577</v>
       </c>
       <c r="C6" t="n">
-        <v>41.35461885054364</v>
+        <v>42.94444001302473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.046218122389578</v>
+        <v>2.09634832665348</v>
       </c>
       <c r="E6" t="n">
-        <v>7.437839066587557</v>
+        <v>8.071959674531554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468439562772405</v>
+        <v>0.7427076440723961</v>
       </c>
       <c r="G6" t="n">
-        <v>31.1858016815078</v>
+        <v>32.11484816823442</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35482198875307</v>
+        <v>34.16455162733022</v>
       </c>
       <c r="I6" t="n">
-        <v>3.79366375676552</v>
+        <v>4.935419279791238</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667774726732754</v>
+        <v>4.641922775452476</v>
       </c>
       <c r="K6" t="n">
-        <v>15.76703670098648</v>
+        <v>13.23224250393424</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75207854767746</v>
+        <v>43.65911483962722</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8737340992076</v>
+        <v>99.83579735658618</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.55014516577369</v>
+        <v>85.42362324138088</v>
       </c>
       <c r="C7" t="n">
-        <v>40.26078243751755</v>
+        <v>42.36720445877796</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964057901255347</v>
+        <v>2.032970438538628</v>
       </c>
       <c r="E7" t="n">
-        <v>7.666764456093075</v>
+        <v>8.514500785778342</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477985599873346</v>
+        <v>0.7439015194907221</v>
       </c>
       <c r="G7" t="n">
-        <v>29.93362219274011</v>
+        <v>31.14393544912491</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39873375941739</v>
+        <v>34.21946989657322</v>
       </c>
       <c r="I7" t="n">
-        <v>3.165427296359589</v>
+        <v>4.119460655058044</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673740999920841</v>
+        <v>4.649384496817014</v>
       </c>
       <c r="K7" t="n">
-        <v>17.44985483422631</v>
+        <v>14.57637675861913</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18398317945709</v>
+        <v>42.91932380260873</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89462045120095</v>
+        <v>99.86290502000581</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.56152382063524</v>
+        <v>83.88257980522883</v>
       </c>
       <c r="C8" t="n">
-        <v>42.54346141148125</v>
+        <v>41.46641206998307</v>
       </c>
       <c r="D8" t="n">
-        <v>1.968369381315557</v>
+        <v>1.960499998983101</v>
       </c>
       <c r="E8" t="n">
-        <v>9.494695580112486</v>
+        <v>8.783908473189769</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494401198305445</v>
+        <v>0.7449177082305312</v>
       </c>
       <c r="G8" t="n">
-        <v>30.4243473068587</v>
+        <v>30.03373008228766</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47424551220504</v>
+        <v>34.26621457860443</v>
       </c>
       <c r="I8" t="n">
-        <v>5.766425171372001</v>
+        <v>3.437573287492518</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684000748940902</v>
+        <v>4.655735676440821</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43847617936476</v>
+        <v>16.11742019477116</v>
       </c>
       <c r="L8" t="n">
-        <v>44.82626925915993</v>
+        <v>42.30173827260527</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80820685000594</v>
+        <v>99.88557053735951</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.52717539677772</v>
+        <v>82.23645165690539</v>
       </c>
       <c r="C9" t="n">
-        <v>41.40339634917254</v>
+        <v>40.35436884874155</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876285446609198</v>
+        <v>1.883545778200311</v>
       </c>
       <c r="E9" t="n">
-        <v>9.852911423593387</v>
+        <v>8.917115229319531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508463327853808</v>
+        <v>0.745783668507762</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00104046339625</v>
+        <v>28.85483577120278</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53893130812752</v>
+        <v>34.30604875135705</v>
       </c>
       <c r="I9" t="n">
-        <v>4.814370842357364</v>
+        <v>2.867974530144419</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69278957990863</v>
+        <v>4.661147928173514</v>
       </c>
       <c r="K9" t="n">
-        <v>14.47282460322228</v>
+        <v>17.76354834309464</v>
       </c>
       <c r="L9" t="n">
-        <v>43.96360057062262</v>
+        <v>41.78659466128902</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83982152301743</v>
+        <v>99.9045118531252</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.38030916652987</v>
+        <v>86.65383700163461</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00288005313045</v>
+        <v>43.40794755087708</v>
       </c>
       <c r="D10" t="n">
-        <v>1.780242879912457</v>
+        <v>1.885664876272231</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01830124006451</v>
+        <v>10.6758988507807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520525394405636</v>
+        <v>0.7466227183213079</v>
       </c>
       <c r="G10" t="n">
-        <v>27.5165465299096</v>
+        <v>30.14859756014369</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59441681426593</v>
+        <v>35.60594347056681</v>
       </c>
       <c r="I10" t="n">
-        <v>4.018420791433296</v>
+        <v>2.924717536041701</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700328371503522</v>
+        <v>4.666391989508176</v>
       </c>
       <c r="K10" t="n">
-        <v>16.61969083347012</v>
+        <v>13.34616299836537</v>
       </c>
       <c r="L10" t="n">
-        <v>43.24369659000062</v>
+        <v>43.14850842551532</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86626747660119</v>
+        <v>99.90261897475777</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23770360163019</v>
+        <v>86.48056834931209</v>
       </c>
       <c r="C11" t="n">
-        <v>38.48265162323762</v>
+        <v>43.59078422491763</v>
       </c>
       <c r="D11" t="n">
-        <v>1.685538646818642</v>
+        <v>1.869872194884008</v>
       </c>
       <c r="E11" t="n">
-        <v>10.04423591409931</v>
+        <v>11.05925490837626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753087301741303</v>
+        <v>0.747335699054405</v>
       </c>
       <c r="G11" t="n">
-        <v>26.05273871699281</v>
+        <v>29.95594805480996</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64201588009994</v>
+        <v>35.69979385526073</v>
       </c>
       <c r="I11" t="n">
-        <v>3.353291505995042</v>
+        <v>2.477515517836697</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706795635883143</v>
+        <v>4.670848119090032</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76229639836982</v>
+        <v>13.51943165068789</v>
       </c>
       <c r="L11" t="n">
-        <v>42.64342917863053</v>
+        <v>42.80727906127711</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88837720023795</v>
+        <v>99.91749493688263</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.04454299882936</v>
+        <v>84.70915187915438</v>
       </c>
       <c r="C12" t="n">
-        <v>36.80817490823944</v>
+        <v>42.20509376444422</v>
       </c>
       <c r="D12" t="n">
-        <v>1.589571396132295</v>
+        <v>1.794092578332815</v>
       </c>
       <c r="E12" t="n">
-        <v>9.938645146922459</v>
+        <v>10.95543974857361</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539757953728787</v>
+        <v>0.7479433473060687</v>
       </c>
       <c r="G12" t="n">
-        <v>24.5694089148322</v>
+        <v>28.74193446434542</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68288658715242</v>
+        <v>35.72882086059227</v>
       </c>
       <c r="I12" t="n">
-        <v>2.79770643733662</v>
+        <v>2.066274959341273</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712348721080491</v>
+        <v>4.674645920662931</v>
       </c>
       <c r="K12" t="n">
-        <v>20.95545700117064</v>
+        <v>15.29084812084562</v>
       </c>
       <c r="L12" t="n">
-        <v>42.14322110431229</v>
+        <v>42.43523823921468</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90685301372235</v>
+        <v>99.93118012450452</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.79871418659341</v>
+        <v>85.82792211048292</v>
       </c>
       <c r="C13" t="n">
-        <v>34.99434277954287</v>
+        <v>43.15868301739678</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492185519915634</v>
+        <v>1.795418270225239</v>
       </c>
       <c r="E13" t="n">
-        <v>9.718713084621035</v>
+        <v>11.58206106312472</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547395305421001</v>
+        <v>0.7484960180230045</v>
       </c>
       <c r="G13" t="n">
-        <v>23.06415194989293</v>
+        <v>29.0645985042419</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71801840493661</v>
+        <v>36.05664765449635</v>
       </c>
       <c r="I13" t="n">
-        <v>2.333783630797005</v>
+        <v>1.902600487727927</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717122065888124</v>
+        <v>4.678100112643779</v>
       </c>
       <c r="K13" t="n">
-        <v>23.20128581340657</v>
+        <v>14.17207788951709</v>
       </c>
       <c r="L13" t="n">
-        <v>41.72665733934677</v>
+        <v>42.60586590458048</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92228593229621</v>
+        <v>99.93662681149434</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.55899517372106</v>
+        <v>84.03308114010184</v>
       </c>
       <c r="C14" t="n">
-        <v>38.99358849503952</v>
+        <v>41.65998295297379</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494160872580554</v>
+        <v>1.720573592754605</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99263968124786</v>
+        <v>11.36366200821376</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7557386534548199</v>
+        <v>0.7489670577446447</v>
       </c>
       <c r="G14" t="n">
-        <v>24.80266893418793</v>
+        <v>27.85299754365316</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47196275791421</v>
+        <v>36.07933864130923</v>
       </c>
       <c r="I14" t="n">
-        <v>3.318457690243059</v>
+        <v>1.586498185522428</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723366584092624</v>
+        <v>4.681044110904031</v>
       </c>
       <c r="K14" t="n">
-        <v>16.44100482627893</v>
+        <v>15.96691885989815</v>
       </c>
       <c r="L14" t="n">
-        <v>44.45493766103865</v>
+        <v>42.32024817358007</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8895309823571</v>
+        <v>99.947149986452</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.11013030586238</v>
+        <v>83.2553111563664</v>
       </c>
       <c r="C15" t="n">
-        <v>39.05724017503512</v>
+        <v>41.12143917016832</v>
       </c>
       <c r="D15" t="n">
-        <v>1.478284525245786</v>
+        <v>1.688424642038559</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32661941724566</v>
+        <v>11.37298024135885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565777914961213</v>
+        <v>0.7493658488970106</v>
       </c>
       <c r="G15" t="n">
-        <v>24.53912583514508</v>
+        <v>27.33256374814695</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51245957682269</v>
+        <v>36.09854926063433</v>
       </c>
       <c r="I15" t="n">
-        <v>2.768451963056286</v>
+        <v>1.32989085968438</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728611196850757</v>
+        <v>4.683536555606318</v>
       </c>
       <c r="K15" t="n">
-        <v>16.88986969413762</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="L15" t="n">
-        <v>43.96071075054272</v>
+        <v>42.08956588187601</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90782061971545</v>
+        <v>99.95569389567792</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.9558125960943</v>
+        <v>80.91602236164118</v>
       </c>
       <c r="C16" t="n">
-        <v>37.33079707645574</v>
+        <v>38.98875274956121</v>
       </c>
       <c r="D16" t="n">
-        <v>1.396555327209588</v>
+        <v>1.591371399851538</v>
       </c>
       <c r="E16" t="n">
-        <v>12.02999641579192</v>
+        <v>10.90403529443264</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572971622615658</v>
+        <v>0.7497081207529014</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18244311218801</v>
+        <v>25.76144599554279</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54717642456692</v>
+        <v>36.11503722504929</v>
       </c>
       <c r="I16" t="n">
-        <v>2.309236889941515</v>
+        <v>1.108748571306395</v>
       </c>
       <c r="J16" t="n">
-        <v>4.733107264134786</v>
+        <v>4.685675754705636</v>
       </c>
       <c r="K16" t="n">
-        <v>19.04418740390569</v>
+        <v>19.08397763835881</v>
       </c>
       <c r="L16" t="n">
-        <v>43.54811407622035</v>
+        <v>41.89032819931096</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92309855658178</v>
+        <v>99.96305858723099</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.84621688800675</v>
+        <v>85.25105697694454</v>
       </c>
       <c r="C17" t="n">
-        <v>38.68300404548086</v>
+        <v>41.81752047518658</v>
       </c>
       <c r="D17" t="n">
-        <v>1.397872360235343</v>
+        <v>1.592175689631757</v>
       </c>
       <c r="E17" t="n">
-        <v>12.89564030648685</v>
+        <v>12.42345257837758</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7580113375996831</v>
+        <v>0.7500870282660846</v>
       </c>
       <c r="G17" t="n">
-        <v>23.66796036733777</v>
+        <v>27.07294003426639</v>
       </c>
       <c r="H17" t="n">
-        <v>37.04529740175323</v>
+        <v>37.43176403823096</v>
       </c>
       <c r="I17" t="n">
-        <v>2.343864254595857</v>
+        <v>1.292593681508748</v>
       </c>
       <c r="J17" t="n">
-        <v>4.737570859998018</v>
+        <v>4.688043926663031</v>
       </c>
       <c r="K17" t="n">
-        <v>17.15378311199325</v>
+        <v>14.74894302305547</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08515764463785</v>
+        <v>43.39047181089128</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92194480211195</v>
+        <v>99.95693530913333</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.79346097824303</v>
+        <v>86.7438730835911</v>
       </c>
       <c r="C18" t="n">
-        <v>36.99226516392311</v>
+        <v>42.5392244398801</v>
       </c>
       <c r="D18" t="n">
-        <v>1.323349227833779</v>
+        <v>1.593411068586795</v>
       </c>
       <c r="E18" t="n">
-        <v>12.53394938113172</v>
+        <v>13.01267564729093</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7586226730222992</v>
+        <v>0.7506690254258213</v>
       </c>
       <c r="G18" t="n">
-        <v>22.40617810859625</v>
+        <v>27.21547514565329</v>
       </c>
       <c r="H18" t="n">
-        <v>37.07517439886354</v>
+        <v>37.46080757522498</v>
       </c>
       <c r="I18" t="n">
-        <v>1.954795482406066</v>
+        <v>2.0191532124979</v>
       </c>
       <c r="J18" t="n">
-        <v>4.741391706389369</v>
+        <v>4.691681408911385</v>
       </c>
       <c r="K18" t="n">
-        <v>19.20653902175698</v>
+        <v>13.2561269164089</v>
       </c>
       <c r="L18" t="n">
-        <v>43.73608847391446</v>
+        <v>44.13739571858788</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93489265959455</v>
+        <v>99.93274707487689</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.0649452768296</v>
+        <v>84.15803798789838</v>
       </c>
       <c r="C19" t="n">
-        <v>36.56508306172707</v>
+        <v>40.26683373744439</v>
       </c>
       <c r="D19" t="n">
-        <v>1.297643841416035</v>
+        <v>1.495887102462973</v>
       </c>
       <c r="E19" t="n">
-        <v>12.56216741013816</v>
+        <v>12.49686599747421</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7591375184624201</v>
+        <v>0.7511696465856246</v>
       </c>
       <c r="G19" t="n">
-        <v>21.97094948238617</v>
+        <v>25.54976494163017</v>
       </c>
       <c r="H19" t="n">
-        <v>37.1003357671692</v>
+        <v>37.48579018713553</v>
       </c>
       <c r="I19" t="n">
-        <v>1.630101766867517</v>
+        <v>1.683749821449722</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744609490390125</v>
+        <v>4.694810291160156</v>
       </c>
       <c r="K19" t="n">
-        <v>19.93505472317037</v>
+        <v>15.84196201210161</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4455623405913</v>
+        <v>43.83511666121795</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94570012548874</v>
+        <v>99.94391241076396</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.78970570232946</v>
+        <v>81.40836883532097</v>
       </c>
       <c r="C20" t="n">
-        <v>34.54106170107867</v>
+        <v>37.77787267744357</v>
       </c>
       <c r="D20" t="n">
-        <v>1.215951748079316</v>
+        <v>1.392667677345379</v>
       </c>
       <c r="E20" t="n">
-        <v>11.99786145158613</v>
+        <v>11.86854395790498</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595796621375974</v>
+        <v>0.7516014575072454</v>
       </c>
       <c r="G20" t="n">
-        <v>20.58778655391049</v>
+        <v>23.7867762476154</v>
       </c>
       <c r="H20" t="n">
-        <v>37.12194407713606</v>
+        <v>37.50733894603702</v>
       </c>
       <c r="I20" t="n">
-        <v>1.359209321119886</v>
+        <v>1.40393143949066</v>
       </c>
       <c r="J20" t="n">
-        <v>4.747372888359983</v>
+        <v>4.697509109420286</v>
       </c>
       <c r="K20" t="n">
-        <v>22.21029429767053</v>
+        <v>18.59163116467904</v>
       </c>
       <c r="L20" t="n">
-        <v>43.20336339661559</v>
+        <v>43.58372532950379</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95471939536479</v>
+        <v>99.95322917162639</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.13635278704284</v>
+        <v>78.63300734532338</v>
       </c>
       <c r="C21" t="n">
-        <v>37.67980261538291</v>
+        <v>35.21921832808247</v>
       </c>
       <c r="D21" t="n">
-        <v>1.216993354242741</v>
+        <v>1.288978575764338</v>
       </c>
       <c r="E21" t="n">
-        <v>13.74682661213353</v>
+        <v>11.17997554040274</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7602303317541712</v>
+        <v>0.7519743997420125</v>
       </c>
       <c r="G21" t="n">
-        <v>21.9880295146847</v>
+        <v>22.01576547545055</v>
       </c>
       <c r="H21" t="n">
-        <v>38.53635049498038</v>
+        <v>37.52594996743271</v>
       </c>
       <c r="I21" t="n">
-        <v>2.136482905783731</v>
+        <v>1.170523388143456</v>
       </c>
       <c r="J21" t="n">
-        <v>4.751439573463569</v>
+        <v>4.69983999838758</v>
       </c>
       <c r="K21" t="n">
-        <v>16.86364721295718</v>
+        <v>21.3669926546766</v>
       </c>
       <c r="L21" t="n">
-        <v>45.38539502757816</v>
+        <v>43.37479092169952</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92884485591824</v>
+        <v>99.96100190445858</v>
       </c>
     </row>
   </sheetData>
